--- a/ig/DM_FINESS_New/CodeSystem-TRE-R16-LieuFormation.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-TRE-R16-LieuFormation.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250709120000</t>
+    <t>20251016120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-09T12:00:00+01:00</t>
+    <t>2025-10-16T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-TRE-R16-LieuFormation.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-TRE-R16-LieuFormation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="57">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251016120000</t>
+    <t>20251222120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-16T12:00:00+01:00</t>
+    <t>2025-12-22T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>1357</t>
+    <t>1360</t>
   </si>
   <si>
     <t>Code</t>
@@ -129,6 +129,9 @@
     <t>dateValid</t>
   </si>
   <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateValid</t>
+  </si>
+  <si>
     <t>date de validité d'un code concept</t>
   </si>
   <si>
@@ -138,10 +141,16 @@
     <t>dateMaj</t>
   </si>
   <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateMaj</t>
+  </si>
+  <si>
     <t>Date de mise à jour d'un code concept</t>
   </si>
   <si>
     <t>dateFin</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateFin</t>
   </si>
   <si>
     <t>Date de fin d'exploitation d'un code concept</t>
@@ -501,78 +510,84 @@
       <c r="A2" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="B2" s="2"/>
+      <c r="B2" t="s" s="2">
+        <v>38</v>
+      </c>
       <c r="C2" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="C3" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="D3" t="s" s="2">
         <v>40</v>
-      </c>
-      <c r="B3" s="2"/>
-      <c r="C3" t="s" s="2">
-        <v>41</v>
-      </c>
-      <c r="D3" t="s" s="2">
-        <v>39</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B4" s="2"/>
+        <v>44</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>45</v>
+      </c>
       <c r="C4" t="s" s="2">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
